--- a/prius2/input/lijst-5_ondraft_v25-08-12.xlsx
+++ b/prius2/input/lijst-5_ondraft_v25-08-12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bram_dhondt\Documents\GitHub\prius\prius2\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7641A13F-102D-4AFE-AFDB-B642125393AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5A6FA1-42E0-4148-B66F-0C9B221DFFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6732" yWindow="0" windowWidth="16200" windowHeight="12360" xr2:uid="{AA2552F2-2547-4780-972A-FBD54CB263EB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AA2552F2-2547-4780-972A-FBD54CB263EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -128,9 +128,6 @@
     <t>soort</t>
   </si>
   <si>
-    <t>lijst</t>
-  </si>
-  <si>
     <t>species_wettelijke_naam_bron</t>
   </si>
   <si>
@@ -197,9 +194,6 @@
     <t>roodoorbuulbuul</t>
   </si>
   <si>
-    <t>zwarte lel</t>
-  </si>
-  <si>
     <t>papiermoerbei</t>
   </si>
   <si>
@@ -216,6 +210,12 @@
   </si>
   <si>
     <t>GBIF_codes</t>
+  </si>
+  <si>
+    <t>Acacia mearnsii</t>
+  </si>
+  <si>
+    <t>reg</t>
   </si>
 </sst>
 </file>
@@ -624,13 +624,13 @@
         <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -638,7 +638,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -658,7 +658,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -678,7 +678,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -718,7 +718,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -738,7 +738,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -749,13 +749,16 @@
       <c r="E7">
         <v>5</v>
       </c>
+      <c r="F7">
+        <v>2440954</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -766,13 +769,16 @@
       <c r="E8">
         <v>5</v>
       </c>
+      <c r="F8">
+        <v>4417558</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
@@ -783,13 +789,16 @@
       <c r="E9">
         <v>5</v>
       </c>
+      <c r="F9">
+        <v>9738098</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -800,13 +809,16 @@
       <c r="E10">
         <v>5</v>
       </c>
+      <c r="F10">
+        <v>8930656</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
@@ -817,13 +829,16 @@
       <c r="E11">
         <v>5</v>
       </c>
+      <c r="F11">
+        <v>2292586</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -834,13 +849,16 @@
       <c r="E12">
         <v>5</v>
       </c>
+      <c r="F12">
+        <v>2367919</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -851,13 +869,16 @@
       <c r="E13">
         <v>5</v>
       </c>
+      <c r="F13">
+        <v>2367913</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>16</v>
@@ -868,13 +889,16 @@
       <c r="E14">
         <v>5</v>
       </c>
+      <c r="F14">
+        <v>2286388</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
@@ -885,13 +909,16 @@
       <c r="E15">
         <v>5</v>
       </c>
+      <c r="F15">
+        <v>5218823</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -902,13 +929,16 @@
       <c r="E16">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <v>8701771</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
@@ -919,13 +949,16 @@
       <c r="E17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <v>5892137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
         <v>21</v>
@@ -936,16 +969,19 @@
       <c r="E18">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <v>2486151</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -953,13 +989,16 @@
       <c r="E19">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <v>5871429</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
         <v>0</v>
@@ -970,13 +1009,16 @@
       <c r="E20">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <v>2979775</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -987,13 +1029,16 @@
       <c r="E21">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <v>5361944</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -1004,13 +1049,16 @@
       <c r="E22">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22">
+        <v>5362054</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -1021,13 +1069,16 @@
       <c r="E23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23">
+        <v>3134183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -1038,13 +1089,16 @@
       <c r="E24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24">
+        <v>2863941</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
         <v>24</v>
@@ -1055,13 +1109,16 @@
       <c r="E25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <v>4038485</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
         <v>22</v>
@@ -1072,13 +1129,16 @@
       <c r="E26">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26">
+        <v>2889173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -1088,6 +1148,9 @@
       </c>
       <c r="E27">
         <v>5</v>
+      </c>
+      <c r="F27">
+        <v>2889088</v>
       </c>
     </row>
   </sheetData>

--- a/prius2/input/lijst-5_ondraft_v25-08-12.xlsx
+++ b/prius2/input/lijst-5_ondraft_v25-08-12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bram_dhondt\Documents\GitHub\prius\prius2\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5A6FA1-42E0-4148-B66F-0C9B221DFFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5462DAFC-8F6E-45B6-852D-A9DA97CEAD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AA2552F2-2547-4780-972A-FBD54CB263EB}"/>
   </bookViews>
@@ -140,9 +140,6 @@
     <t>Canadese bever</t>
   </si>
   <si>
-    <t>Noord-Aziatische modderkruiper  </t>
-  </si>
-  <si>
     <t>Amerikaanse strandschelp</t>
   </si>
   <si>
@@ -185,9 +182,6 @@
     <t>marisaslak</t>
   </si>
   <si>
-    <t>Aziatische Modderkruiper</t>
-  </si>
-  <si>
     <t>grote gevlekte landplatworm</t>
   </si>
   <si>
@@ -216,13 +210,19 @@
   </si>
   <si>
     <t>reg</t>
+  </si>
+  <si>
+    <t>Noord-Aziatische modderkruiper</t>
+  </si>
+  <si>
+    <t>Aziatische modderkruiper</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,12 +234,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -265,10 +259,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -624,13 +617,13 @@
         <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -638,7 +631,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -678,7 +671,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -738,7 +731,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -758,7 +751,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -778,7 +771,7 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
@@ -798,7 +791,7 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -818,7 +811,7 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
@@ -838,7 +831,7 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -858,7 +851,7 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -870,7 +863,7 @@
         <v>5</v>
       </c>
       <c r="F13">
-        <v>2367913</v>
+        <v>2367911</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -878,7 +871,7 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
         <v>16</v>
@@ -898,7 +891,7 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
@@ -918,7 +911,7 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -938,7 +931,7 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
@@ -958,7 +951,7 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
         <v>21</v>
@@ -977,11 +970,11 @@
       <c r="A19" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>41</v>
+      <c r="B19" t="s">
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -998,7 +991,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
         <v>0</v>
@@ -1018,7 +1011,7 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -1038,7 +1031,7 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -1058,7 +1051,7 @@
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -1078,7 +1071,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -1098,7 +1091,7 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s">
         <v>24</v>
@@ -1118,7 +1111,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
         <v>22</v>
@@ -1138,7 +1131,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
